--- a/docs/d/202/inyear.xlsx
+++ b/docs/d/202/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 55 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 52 clubs short</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
         <v>0</v>
       </c>
       <c r="Q2" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" s="9" t="n">
         <v>0</v>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>10</v>
@@ -1488,8 +1488,8 @@
       <c r="Y8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z8" s="9" t="n">
-        <v>0</v>
+      <c r="Z8" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA8" s="10" t="n">
         <v>1</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F67" s="6" t="n">
         <v>10</v>
@@ -7211,8 +7211,8 @@
       <c r="Y67" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z67" s="9" t="n">
-        <v>0</v>
+      <c r="Z67" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA67" s="10" t="n">
         <v>1</v>
@@ -14125,7 +14125,7 @@
         </is>
       </c>
       <c r="E139" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F139" s="6" t="n">
         <v>10</v>
@@ -14195,8 +14195,8 @@
       <c r="Y139" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z139" s="9" t="n">
-        <v>0</v>
+      <c r="Z139" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA139" s="10" t="n">
         <v>1</v>
@@ -15196,7 +15196,7 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -15592,7 +15592,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -16021,7 +16021,7 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>

--- a/docs/d/202/inyear.xlsx
+++ b/docs/d/202/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:40 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/202/inyear.xlsx
+++ b/docs/d/202/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 10 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 10 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 52 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 49 clubs short</t>
         </is>
       </c>
     </row>
@@ -1141,13 +1141,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>0</v>
       </c>
       <c r="V5" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W5" s="9" t="n">
         <v>0</v>
@@ -3649,7 +3649,7 @@
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>10</v>
@@ -3719,8 +3719,8 @@
       <c r="Y31" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z31" s="9" t="n">
-        <v>0</v>
+      <c r="Z31" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA31" s="10" t="n">
         <v>1</v>
@@ -3843,7 +3843,7 @@
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33" s="6" t="n">
         <v>10</v>
@@ -3913,8 +3913,8 @@
       <c r="Y33" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z33" s="9" t="n">
-        <v>0</v>
+      <c r="Z33" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA33" s="10" t="n">
         <v>1</v>
@@ -4231,7 +4231,7 @@
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37" s="6" t="n">
         <v>10</v>
@@ -4271,8 +4271,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P37" s="9" t="n">
-        <v>3</v>
+      <c r="P37" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q37" s="9" t="n">
         <v>0</v>
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="P60" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q60" s="9" t="n">
         <v>0</v>
@@ -10580,7 +10580,7 @@
         <v>0</v>
       </c>
       <c r="Q102" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R102" s="9" t="n">
         <v>0</v>
@@ -12864,7 +12864,7 @@
         </is>
       </c>
       <c r="E126" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F126" s="6" t="n">
         <v>10</v>
@@ -12934,8 +12934,8 @@
       <c r="Y126" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z126" s="9" t="n">
-        <v>0</v>
+      <c r="Z126" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA126" s="10" t="n">
         <v>1</v>
@@ -13737,7 +13737,7 @@
         </is>
       </c>
       <c r="E135" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F135" s="6" t="n">
         <v>10</v>
@@ -13789,8 +13789,8 @@
       <c r="S135" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T135" s="9" t="n">
-        <v>0</v>
+      <c r="T135" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U135" s="9" t="n">
         <v>0</v>
@@ -15328,7 +15328,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -15361,7 +15361,7 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -15394,7 +15394,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -15988,7 +15988,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>

--- a/docs/d/202/inyear.xlsx
+++ b/docs/d/202/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 10 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 10 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 49 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 25 clubs short</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="6" t="n">
         <v>10</v>
@@ -906,8 +906,8 @@
       <c r="Y2" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z2" s="9" t="n">
-        <v>0</v>
+      <c r="Z2" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA2" s="10" t="n">
         <v>1</v>
@@ -977,7 +977,7 @@
         <v>0</v>
       </c>
       <c r="Q3" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" s="9" t="n">
         <v>0</v>
@@ -1294,8 +1294,8 @@
       <c r="Y6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z6" s="9" t="n">
-        <v>0</v>
+      <c r="Z6" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA6" s="9" t="n">
         <v>0</v>
@@ -1612,7 +1612,7 @@
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>10</v>
@@ -1653,13 +1653,13 @@
         </is>
       </c>
       <c r="P10" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="Q10" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R10" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" s="9" t="n">
         <v>1</v>
@@ -1709,7 +1709,7 @@
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>10</v>
@@ -1723,13 +1723,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>0</v>
       </c>
       <c r="V11" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W11" s="9" t="n">
         <v>0</v>
@@ -1779,8 +1779,8 @@
       <c r="Y11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z11" s="9" t="n">
-        <v>0</v>
+      <c r="Z11" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA11" s="10" t="n">
         <v>1</v>
@@ -1806,7 +1806,7 @@
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>10</v>
@@ -1876,8 +1876,8 @@
       <c r="Y12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z12" s="9" t="n">
-        <v>0</v>
+      <c r="Z12" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA12" s="10" t="n">
         <v>1</v>
@@ -2138,7 +2138,7 @@
         </is>
       </c>
       <c r="P15" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q15" s="9" t="n">
         <v>0</v>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>10</v>
@@ -3137,8 +3137,8 @@
       <c r="Y25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z25" s="9" t="n">
-        <v>0</v>
+      <c r="Z25" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA25" s="10" t="n">
         <v>1</v>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26" s="6" t="n">
         <v>10</v>
@@ -3234,8 +3234,8 @@
       <c r="Y26" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z26" s="9" t="n">
-        <v>0</v>
+      <c r="Z26" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA26" s="10" t="n">
         <v>1</v>
@@ -3552,7 +3552,7 @@
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>10</v>
@@ -3622,8 +3622,8 @@
       <c r="Y30" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z30" s="9" t="n">
-        <v>0</v>
+      <c r="Z30" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA30" s="10" t="n">
         <v>1</v>
@@ -3940,7 +3940,7 @@
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F34" s="6" t="n">
         <v>10</v>
@@ -3954,17 +3954,17 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M34" s="8" t="n">
@@ -3998,11 +3998,11 @@
       <c r="U34" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V34" s="9" t="n">
-        <v>0</v>
+      <c r="V34" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W34" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X34" s="10" t="n">
         <v>4</v>
@@ -4010,8 +4010,8 @@
       <c r="Y34" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z34" s="9" t="n">
-        <v>0</v>
+      <c r="Z34" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA34" s="10" t="n">
         <v>1</v>
@@ -4231,7 +4231,7 @@
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F37" s="6" t="n">
         <v>10</v>
@@ -4301,8 +4301,8 @@
       <c r="Y37" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z37" s="9" t="n">
-        <v>0</v>
+      <c r="Z37" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA37" s="10" t="n">
         <v>1</v>
@@ -4716,7 +4716,7 @@
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42" s="6" t="n">
         <v>10</v>
@@ -4786,8 +4786,8 @@
       <c r="Y42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z42" s="9" t="n">
-        <v>0</v>
+      <c r="Z42" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA42" s="10" t="n">
         <v>1</v>
@@ -4910,7 +4910,7 @@
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F44" s="6" t="n">
         <v>10</v>
@@ -4980,8 +4980,8 @@
       <c r="Y44" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z44" s="9" t="n">
-        <v>0</v>
+      <c r="Z44" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA44" s="10" t="n">
         <v>1</v>
@@ -5048,7 +5048,7 @@
         </is>
       </c>
       <c r="P45" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q45" s="9" t="n">
         <v>1</v>
@@ -6241,8 +6241,8 @@
       <c r="Y57" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z57" s="9" t="n">
-        <v>0</v>
+      <c r="Z57" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA57" s="9" t="n">
         <v>0</v>
@@ -6365,7 +6365,7 @@
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F59" s="6" t="n">
         <v>10</v>
@@ -6435,8 +6435,8 @@
       <c r="Y59" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z59" s="9" t="n">
-        <v>0</v>
+      <c r="Z59" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA59" s="10" t="n">
         <v>1</v>
@@ -6864,13 +6864,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>41</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>4</v>
       </c>
       <c r="W64" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X64" s="9" t="n">
         <v>0</v>
@@ -7238,7 +7238,7 @@
         </is>
       </c>
       <c r="E68" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F68" s="6" t="n">
         <v>10</v>
@@ -7288,7 +7288,7 @@
         <v>0</v>
       </c>
       <c r="S68" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T68" s="9" t="n">
         <v>0</v>
@@ -7308,8 +7308,8 @@
       <c r="Y68" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z68" s="9" t="n">
-        <v>0</v>
+      <c r="Z68" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA68" s="10" t="n">
         <v>1</v>
@@ -7626,7 +7626,7 @@
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F72" s="6" t="n">
         <v>10</v>
@@ -7667,7 +7667,7 @@
         </is>
       </c>
       <c r="P72" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q72" s="9" t="n">
         <v>0</v>
@@ -7696,8 +7696,8 @@
       <c r="Y72" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z72" s="9" t="n">
-        <v>0</v>
+      <c r="Z72" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA72" s="10" t="n">
         <v>1</v>
@@ -8540,10 +8540,10 @@
         </is>
       </c>
       <c r="P81" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q81" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R81" s="9" t="n">
         <v>0</v>
@@ -9372,7 +9372,7 @@
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F90" s="6" t="n">
         <v>10</v>
@@ -9415,8 +9415,8 @@
       <c r="P90" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q90" s="9" t="n">
-        <v>1</v>
+      <c r="Q90" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R90" s="9" t="n">
         <v>0</v>
@@ -9760,7 +9760,7 @@
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>10</v>
@@ -9830,8 +9830,8 @@
       <c r="Y94" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z94" s="9" t="n">
-        <v>0</v>
+      <c r="Z94" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA94" s="10" t="n">
         <v>1</v>
@@ -10289,7 +10289,7 @@
         <v>2</v>
       </c>
       <c r="Q99" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R99" s="9" t="n">
         <v>0</v>
@@ -10536,7 +10536,7 @@
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F102" s="6" t="n">
         <v>10</v>
@@ -10606,8 +10606,8 @@
       <c r="Y102" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z102" s="9" t="n">
-        <v>0</v>
+      <c r="Z102" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA102" s="10" t="n">
         <v>1</v>
@@ -12032,7 +12032,7 @@
         </is>
       </c>
       <c r="P117" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q117" s="9" t="n">
         <v>0</v>
@@ -12420,7 +12420,7 @@
         </is>
       </c>
       <c r="P121" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q121" s="9" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
         </is>
       </c>
       <c r="E123" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F123" s="6" t="n">
         <v>10</v>
@@ -12628,8 +12628,8 @@
       <c r="T123" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U123" s="9" t="n">
-        <v>0</v>
+      <c r="U123" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V123" s="9" t="n">
         <v>0</v>
@@ -12767,7 +12767,7 @@
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F125" s="6" t="n">
         <v>10</v>
@@ -12837,8 +12837,8 @@
       <c r="Y125" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z125" s="9" t="n">
-        <v>0</v>
+      <c r="Z125" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA125" s="10" t="n">
         <v>1</v>
@@ -12961,7 +12961,7 @@
         </is>
       </c>
       <c r="E127" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F127" s="6" t="n">
         <v>10</v>
@@ -13005,7 +13005,7 @@
         <v>1</v>
       </c>
       <c r="Q127" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R127" s="9" t="n">
         <v>0</v>
@@ -13031,8 +13031,8 @@
       <c r="Y127" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z127" s="9" t="n">
-        <v>0</v>
+      <c r="Z127" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA127" s="10" t="n">
         <v>1</v>
@@ -13640,7 +13640,7 @@
         </is>
       </c>
       <c r="E134" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F134" s="6" t="n">
         <v>10</v>
@@ -13710,8 +13710,8 @@
       <c r="Y134" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z134" s="9" t="n">
-        <v>0</v>
+      <c r="Z134" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA134" s="10" t="n">
         <v>1</v>
@@ -13834,7 +13834,7 @@
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F136" s="6" t="n">
         <v>10</v>
@@ -13904,8 +13904,8 @@
       <c r="Y136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z136" s="9" t="n">
-        <v>0</v>
+      <c r="Z136" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA136" s="10" t="n">
         <v>1</v>
@@ -14319,7 +14319,7 @@
         </is>
       </c>
       <c r="E141" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F141" s="6" t="n">
         <v>10</v>
@@ -14389,8 +14389,8 @@
       <c r="Y141" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z141" s="9" t="n">
-        <v>0</v>
+      <c r="Z141" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA141" s="10" t="n">
         <v>1</v>
@@ -14901,7 +14901,7 @@
         </is>
       </c>
       <c r="E147" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F147" s="6" t="n">
         <v>10</v>
@@ -14971,8 +14971,8 @@
       <c r="Y147" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z147" s="9" t="n">
-        <v>0</v>
+      <c r="Z147" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA147" s="10" t="n">
         <v>1</v>
@@ -14998,7 +14998,7 @@
         </is>
       </c>
       <c r="E148" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F148" s="6" t="n">
         <v>10</v>
@@ -15068,8 +15068,8 @@
       <c r="Y148" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z148" s="9" t="n">
-        <v>0</v>
+      <c r="Z148" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA148" s="10" t="n">
         <v>1</v>
@@ -15163,7 +15163,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -15196,7 +15196,7 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>1.17</v>
+        <v>1.67</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -15295,7 +15295,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -15328,7 +15328,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -15361,7 +15361,7 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -15376,7 +15376,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -15394,7 +15394,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -15427,7 +15427,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -15526,7 +15526,7 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -15592,7 +15592,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -15625,7 +15625,7 @@
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -15724,7 +15724,7 @@
         <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -15790,7 +15790,7 @@
         <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -15955,7 +15955,7 @@
         <v>6</v>
       </c>
       <c r="D26" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -15988,7 +15988,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -16021,7 +16021,7 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -16054,7 +16054,7 @@
         <v>6</v>
       </c>
       <c r="D29" t="n">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>

--- a/docs/d/202/inyear.xlsx
+++ b/docs/d/202/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 10 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 10 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 25 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 25 clubs short</t>
         </is>
       </c>
     </row>
@@ -850,13 +850,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
@@ -947,13 +947,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>10</v>
@@ -1044,17 +1044,17 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L4" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M4" s="8" t="n">
@@ -1082,14 +1082,14 @@
       <c r="S4" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T4" s="9" t="n">
-        <v>0</v>
+      <c r="T4" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U4" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V4" s="9" t="n">
-        <v>3</v>
+      <c r="V4" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W4" s="9" t="n">
         <v>0</v>
@@ -1141,13 +1141,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
@@ -1238,13 +1238,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
@@ -1335,13 +1335,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
@@ -1432,13 +1432,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>0</v>
       </c>
       <c r="V8" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W8" s="9" t="n">
         <v>0</v>
@@ -1529,13 +1529,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>10</v>
@@ -1626,13 +1626,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
@@ -1661,8 +1661,8 @@
       <c r="R10" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="S10" s="9" t="n">
-        <v>1</v>
+      <c r="S10" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T10" s="10" t="n">
         <v>1</v>
@@ -1723,13 +1723,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>0</v>
       </c>
       <c r="V11" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W11" s="9" t="n">
         <v>0</v>
@@ -1865,7 +1865,7 @@
         <v>0</v>
       </c>
       <c r="V12" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W12" s="9" t="n">
         <v>0</v>
@@ -2059,7 +2059,7 @@
         <v>0</v>
       </c>
       <c r="V14" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W14" s="9" t="n">
         <v>0</v>
@@ -2111,13 +2111,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
@@ -2208,13 +2208,13 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L16" s="7" t="inlineStr">
         <is>
@@ -2305,13 +2305,13 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>2</v>
+        <v>-6</v>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
@@ -2350,7 +2350,7 @@
         <v>0</v>
       </c>
       <c r="V17" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W17" s="9" t="n">
         <v>0</v>
@@ -2499,13 +2499,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>4</v>
+        <v>-10</v>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
@@ -2596,13 +2596,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
@@ -2693,13 +2693,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
@@ -2790,13 +2790,13 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>4</v>
+        <v>-3</v>
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
@@ -2984,13 +2984,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" s="7" t="inlineStr">
         <is>
@@ -3081,17 +3081,17 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L25" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M25" s="8" t="n">
@@ -3178,13 +3178,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L26" s="7" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>0</v>
       </c>
       <c r="V26" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W26" s="9" t="n">
         <v>0</v>
@@ -3275,17 +3275,17 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L27" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L27" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M27" s="8" t="n">
@@ -3372,13 +3372,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L28" s="7" t="inlineStr">
         <is>
@@ -3469,13 +3469,13 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         </is>
       </c>
       <c r="P29" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q29" s="9" t="n">
         <v>0</v>
@@ -3611,7 +3611,7 @@
         <v>0</v>
       </c>
       <c r="V30" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W30" s="9" t="n">
         <v>0</v>
@@ -3663,13 +3663,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="V31" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W31" s="9" t="n">
         <v>0</v>
@@ -3760,13 +3760,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L32" s="7" t="inlineStr">
         <is>
@@ -3857,13 +3857,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
@@ -3954,17 +3954,17 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L34" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L34" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M34" s="8" t="n">
@@ -4051,17 +4051,17 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L35" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M35" s="8" t="n">
@@ -4148,13 +4148,13 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L36" s="7" t="inlineStr">
         <is>
@@ -4245,17 +4245,17 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L37" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M37" s="8" t="n">
@@ -4342,13 +4342,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
@@ -4536,13 +4536,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L40" s="7" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
@@ -4730,13 +4730,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L42" s="7" t="inlineStr">
         <is>
@@ -4827,13 +4827,13 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>10</v>
@@ -5021,13 +5021,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
@@ -5050,20 +5050,20 @@
       <c r="P45" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q45" s="9" t="n">
-        <v>1</v>
+      <c r="Q45" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R45" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S45" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T45" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U45" s="9" t="n">
-        <v>0</v>
+      <c r="S45" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T45" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V45" s="9" t="n">
         <v>0</v>
@@ -5118,13 +5118,13 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L46" s="7" t="inlineStr">
         <is>
@@ -5215,13 +5215,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         <v>0</v>
       </c>
       <c r="V47" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W47" s="9" t="n">
         <v>0</v>
@@ -5312,13 +5312,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
@@ -5506,13 +5506,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L52" s="7" t="inlineStr">
         <is>
@@ -5797,13 +5797,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
@@ -5894,13 +5894,13 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>4</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L54" s="7" t="inlineStr">
         <is>
@@ -5977,7 +5977,7 @@
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F55" s="6" t="n">
         <v>10</v>
@@ -5991,13 +5991,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>39</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
@@ -6035,8 +6035,8 @@
       <c r="U55" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V55" s="9" t="n">
-        <v>2</v>
+      <c r="V55" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W55" s="9" t="n">
         <v>0</v>
@@ -6088,13 +6088,13 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L56" s="7" t="inlineStr">
         <is>
@@ -6185,13 +6185,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
@@ -6282,13 +6282,13 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
@@ -6476,17 +6476,17 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L60" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L60" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M60" s="8" t="n">
@@ -6573,13 +6573,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
@@ -6670,13 +6670,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
@@ -6715,7 +6715,7 @@
         <v>0</v>
       </c>
       <c r="V62" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W62" s="9" t="n">
         <v>0</v>
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
@@ -6864,13 +6864,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>41</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>7</v>
+        <v>-14</v>
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
@@ -6961,13 +6961,13 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
@@ -7058,13 +7058,13 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
@@ -7252,13 +7252,13 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L68" s="7" t="inlineStr">
         <is>
@@ -7297,7 +7297,7 @@
         <v>0</v>
       </c>
       <c r="V68" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W68" s="9" t="n">
         <v>0</v>
@@ -7349,17 +7349,17 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L69" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M69" s="8" t="n">
@@ -7446,13 +7446,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
@@ -7473,7 +7473,7 @@
         </is>
       </c>
       <c r="P70" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q70" s="9" t="n">
         <v>0</v>
@@ -7543,13 +7543,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>5</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
@@ -7626,7 +7626,7 @@
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F72" s="6" t="n">
         <v>10</v>
@@ -7640,13 +7640,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
@@ -7670,16 +7670,16 @@
         <v>2</v>
       </c>
       <c r="Q72" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R72" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S72" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T72" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T72" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U72" s="9" t="n">
         <v>0</v>
@@ -7737,13 +7737,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>4</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
@@ -7834,17 +7834,17 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L74" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L74" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M74" s="8" t="n">
@@ -7870,7 +7870,7 @@
         <v>0</v>
       </c>
       <c r="S74" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T74" s="9" t="n">
         <v>0</v>
@@ -7931,13 +7931,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
@@ -8028,13 +8028,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="L76" s="7" t="inlineStr">
         <is>
@@ -8125,13 +8125,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>2</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
@@ -8222,13 +8222,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
@@ -8319,17 +8319,17 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L79" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L79" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M79" s="8" t="n">
@@ -8416,17 +8416,17 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L80" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L80" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M80" s="8" t="n">
@@ -8461,7 +8461,7 @@
         <v>1</v>
       </c>
       <c r="V80" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W80" s="9" t="n">
         <v>0</v>
@@ -8513,17 +8513,17 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L81" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L81" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M81" s="8" t="n">
@@ -8558,7 +8558,7 @@
         <v>0</v>
       </c>
       <c r="V81" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W81" s="9" t="n">
         <v>0</v>
@@ -8610,13 +8610,13 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L82" s="7" t="inlineStr">
         <is>
@@ -8707,13 +8707,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
@@ -8804,13 +8804,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L84" s="7" t="inlineStr">
         <is>
@@ -8946,7 +8946,7 @@
         <v>0</v>
       </c>
       <c r="V85" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W85" s="9" t="n">
         <v>0</v>
@@ -8998,13 +8998,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L86" s="4" t="inlineStr">
         <is>
@@ -9095,13 +9095,13 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L87" s="4" t="inlineStr">
         <is>
@@ -9192,13 +9192,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L88" s="7" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
         <v>0</v>
       </c>
       <c r="V88" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W88" s="9" t="n">
         <v>0</v>
@@ -9289,17 +9289,17 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L89" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L89" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M89" s="8" t="n">
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L90" s="7" t="inlineStr">
         <is>
@@ -9483,17 +9483,17 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L91" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L91" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M91" s="8" t="n">
@@ -9528,7 +9528,7 @@
         <v>0</v>
       </c>
       <c r="V91" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W91" s="9" t="n">
         <v>0</v>
@@ -9625,7 +9625,7 @@
         <v>0</v>
       </c>
       <c r="V92" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W92" s="9" t="n">
         <v>0</v>
@@ -9677,17 +9677,17 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L93" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L93" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M93" s="8" t="n">
@@ -9774,13 +9774,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L94" s="7" t="inlineStr">
         <is>
@@ -9819,7 +9819,7 @@
         <v>0</v>
       </c>
       <c r="V94" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W94" s="9" t="n">
         <v>0</v>
@@ -9871,13 +9871,13 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L95" s="7" t="inlineStr">
         <is>
@@ -9898,7 +9898,7 @@
         </is>
       </c>
       <c r="P95" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q95" s="10" t="n">
         <v>2</v>
@@ -9968,13 +9968,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L96" s="7" t="inlineStr">
         <is>
@@ -10013,7 +10013,7 @@
         <v>0</v>
       </c>
       <c r="V96" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W96" s="9" t="n">
         <v>0</v>
@@ -10065,13 +10065,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L97" s="7" t="inlineStr">
         <is>
@@ -10110,7 +10110,7 @@
         <v>0</v>
       </c>
       <c r="V97" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W97" s="9" t="n">
         <v>0</v>
@@ -10148,7 +10148,7 @@
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F98" s="6" t="n">
         <v>10</v>
@@ -10162,17 +10162,17 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L98" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L98" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M98" s="8" t="n">
@@ -10206,8 +10206,8 @@
       <c r="U98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V98" s="9" t="n">
-        <v>2</v>
+      <c r="V98" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W98" s="9" t="n">
         <v>0</v>
@@ -10356,13 +10356,13 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L100" s="7" t="inlineStr">
         <is>
@@ -10401,7 +10401,7 @@
         <v>0</v>
       </c>
       <c r="V100" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W100" s="9" t="n">
         <v>0</v>
@@ -10453,13 +10453,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
@@ -10595,7 +10595,7 @@
         <v>0</v>
       </c>
       <c r="V102" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W102" s="9" t="n">
         <v>0</v>
@@ -10647,17 +10647,17 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L103" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L103" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M103" s="8" t="n">
@@ -10744,13 +10744,13 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L104" s="7" t="inlineStr">
         <is>
@@ -10841,13 +10841,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L105" s="7" t="inlineStr">
         <is>
@@ -10877,7 +10877,7 @@
         <v>0</v>
       </c>
       <c r="S105" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T105" s="9" t="n">
         <v>0</v>
@@ -10938,13 +10938,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L106" s="7" t="inlineStr">
         <is>
@@ -10983,7 +10983,7 @@
         <v>0</v>
       </c>
       <c r="V106" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W106" s="9" t="n">
         <v>0</v>
@@ -11035,13 +11035,13 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L107" s="7" t="inlineStr">
         <is>
@@ -11080,7 +11080,7 @@
         <v>0</v>
       </c>
       <c r="V107" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W107" s="9" t="n">
         <v>0</v>
@@ -11132,13 +11132,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L108" s="7" t="inlineStr">
         <is>
@@ -11177,7 +11177,7 @@
         <v>0</v>
       </c>
       <c r="V108" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W108" s="9" t="n">
         <v>0</v>
@@ -11229,13 +11229,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L109" s="4" t="inlineStr">
         <is>
@@ -11312,7 +11312,7 @@
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F110" s="6" t="n">
         <v>10</v>
@@ -11326,13 +11326,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>39</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>3</v>
+        <v>-7</v>
       </c>
       <c r="L110" s="4" t="inlineStr">
         <is>
@@ -11370,8 +11370,8 @@
       <c r="U110" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V110" s="9" t="n">
-        <v>3</v>
+      <c r="V110" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W110" s="9" t="n">
         <v>0</v>
@@ -11423,13 +11423,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L111" s="7" t="inlineStr">
         <is>
@@ -11468,7 +11468,7 @@
         <v>0</v>
       </c>
       <c r="V111" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W111" s="9" t="n">
         <v>0</v>
@@ -11520,17 +11520,17 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L112" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L112" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M112" s="8" t="n">
@@ -11547,7 +11547,7 @@
         </is>
       </c>
       <c r="P112" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q112" s="9" t="n">
         <v>1</v>
@@ -11617,13 +11617,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L113" s="4" t="inlineStr">
         <is>
@@ -11714,13 +11714,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>3</v>
+        <v>-10</v>
       </c>
       <c r="L114" s="4" t="inlineStr">
         <is>
@@ -11811,13 +11811,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>1</v>
+        <v>-8</v>
       </c>
       <c r="L115" s="7" t="inlineStr">
         <is>
@@ -11908,13 +11908,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L116" s="7" t="inlineStr">
         <is>
@@ -12005,17 +12005,17 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L117" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L117" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M117" s="8" t="n">
@@ -12102,13 +12102,13 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L118" s="7" t="inlineStr">
         <is>
@@ -12199,17 +12199,17 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L119" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L119" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M119" s="8" t="n">
@@ -12296,13 +12296,13 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L120" s="7" t="inlineStr">
         <is>
@@ -12393,13 +12393,13 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L121" s="4" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
         <v>0</v>
       </c>
       <c r="V121" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W121" s="9" t="n">
         <v>0</v>
@@ -12490,13 +12490,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L122" s="7" t="inlineStr">
         <is>
@@ -12670,7 +12670,7 @@
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F124" s="6" t="n">
         <v>10</v>
@@ -12684,17 +12684,17 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L124" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L124" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M124" s="8" t="n">
@@ -12725,8 +12725,8 @@
       <c r="T124" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U124" s="9" t="n">
-        <v>0</v>
+      <c r="U124" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V124" s="9" t="n">
         <v>0</v>
@@ -12781,13 +12781,13 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J125" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L125" s="7" t="inlineStr">
         <is>
@@ -12878,13 +12878,13 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L126" s="7" t="inlineStr">
         <is>
@@ -13020,7 +13020,7 @@
         <v>0</v>
       </c>
       <c r="V127" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W127" s="9" t="n">
         <v>0</v>
@@ -13072,13 +13072,13 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J128" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L128" s="4" t="inlineStr">
         <is>
@@ -13169,13 +13169,13 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J129" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L129" s="7" t="inlineStr">
         <is>
@@ -13266,13 +13266,13 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L130" s="7" t="inlineStr">
         <is>
@@ -13408,7 +13408,7 @@
         <v>0</v>
       </c>
       <c r="V131" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W131" s="9" t="n">
         <v>0</v>
@@ -13460,17 +13460,17 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L132" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L132" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M132" s="8" t="n">
@@ -13557,13 +13557,13 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J133" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L133" s="7" t="inlineStr">
         <is>
@@ -13654,13 +13654,13 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J134" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L134" s="7" t="inlineStr">
         <is>
@@ -13751,13 +13751,13 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="J135" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L135" s="4" t="inlineStr">
         <is>
@@ -13848,13 +13848,13 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L136" s="7" t="inlineStr">
         <is>
@@ -13945,17 +13945,17 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J137" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L137" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L137" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M137" s="8" t="n">
@@ -13972,7 +13972,7 @@
         </is>
       </c>
       <c r="P137" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q137" s="9" t="n">
         <v>0</v>
@@ -13990,7 +13990,7 @@
         <v>0</v>
       </c>
       <c r="V137" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W137" s="9" t="n">
         <v>0</v>
@@ -14028,7 +14028,7 @@
         </is>
       </c>
       <c r="E138" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F138" s="6" t="n">
         <v>10</v>
@@ -14042,13 +14042,13 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J138" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L138" s="7" t="inlineStr">
         <is>
@@ -14077,8 +14077,8 @@
       <c r="R138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S138" s="9" t="n">
-        <v>1</v>
+      <c r="S138" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T138" s="9" t="n">
         <v>0</v>
@@ -14139,13 +14139,13 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J139" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L139" s="7" t="inlineStr">
         <is>
@@ -14184,7 +14184,7 @@
         <v>0</v>
       </c>
       <c r="V139" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W139" s="9" t="n">
         <v>0</v>
@@ -14222,7 +14222,7 @@
         </is>
       </c>
       <c r="E140" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F140" s="6" t="n">
         <v>10</v>
@@ -14236,13 +14236,13 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J140" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L140" s="4" t="inlineStr">
         <is>
@@ -14280,8 +14280,8 @@
       <c r="U140" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V140" s="9" t="n">
-        <v>0</v>
+      <c r="V140" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W140" s="9" t="n">
         <v>0</v>
@@ -14333,13 +14333,13 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J141" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L141" s="7" t="inlineStr">
         <is>
@@ -14430,17 +14430,17 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="J142" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L142" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L142" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M142" s="8" t="n">
@@ -14527,13 +14527,13 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="J143" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>4</v>
+        <v>-8</v>
       </c>
       <c r="L143" s="4" t="inlineStr">
         <is>
@@ -14624,17 +14624,17 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J144" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L144" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L144" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M144" s="8" t="n">
@@ -14721,13 +14721,13 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J145" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K145" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L145" s="7" t="inlineStr">
         <is>
@@ -14818,13 +14818,13 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J146" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K146" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L146" s="7" t="inlineStr">
         <is>
@@ -14915,13 +14915,13 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J147" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K147" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L147" s="7" t="inlineStr">
         <is>
@@ -15012,13 +15012,13 @@
         </is>
       </c>
       <c r="I148" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J148" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K148" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L148" s="7" t="inlineStr">
         <is>
@@ -15163,7 +15163,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -15178,7 +15178,7 @@
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -15196,13 +15196,13 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -15310,7 +15310,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -15376,7 +15376,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -15409,7 +15409,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -15427,13 +15427,13 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -15493,13 +15493,13 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -15541,7 +15541,7 @@
         <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -15607,7 +15607,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -15625,7 +15625,7 @@
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -15640,7 +15640,7 @@
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -15673,7 +15673,7 @@
         <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -15739,7 +15739,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -15757,7 +15757,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -15772,7 +15772,7 @@
         <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -15805,7 +15805,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -15823,7 +15823,7 @@
         <v>6</v>
       </c>
       <c r="D22" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -15871,7 +15871,7 @@
         <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -15904,7 +15904,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -15922,7 +15922,7 @@
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -15937,7 +15937,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -15970,7 +15970,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -16003,7 +16003,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -16021,13 +16021,13 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -16036,7 +16036,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -16069,7 +16069,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docs/d/202/inyear.xlsx
+++ b/docs/d/202/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/202/inyear.xlsx
+++ b/docs/d/202/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/202/inyear.xlsx
+++ b/docs/d/202/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/202/inyear.xlsx
+++ b/docs/d/202/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/202/inyear.xlsx
+++ b/docs/d/202/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:49 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 11 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 11 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 25 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 25 clubs short</t>
         </is>
       </c>
     </row>
@@ -1532,10 +1532,10 @@
         <v>16</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L9" s="8" t="inlineStr">
         <is>
@@ -2111,13 +2111,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L15" s="8" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>4</v>
       </c>
       <c r="W15" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X15" s="10" t="n">
         <v>4</v>
@@ -2405,10 +2405,10 @@
         <v>21</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
@@ -2599,10 +2599,10 @@
         <v>14</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L20" s="8" t="inlineStr">
         <is>
@@ -2790,13 +2790,13 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L22" s="8" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>0</v>
       </c>
       <c r="V22" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W22" s="9" t="n">
         <v>0</v>
@@ -2914,7 +2914,7 @@
         </is>
       </c>
       <c r="P23" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q23" s="9" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>11</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L25" s="8" t="inlineStr">
         <is>
@@ -4178,7 +4178,7 @@
         <v>1</v>
       </c>
       <c r="Q36" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R36" s="9" t="n">
         <v>0</v>
@@ -4425,7 +4425,7 @@
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F39" s="6" t="n">
         <v>10</v>
@@ -4474,8 +4474,8 @@
       <c r="R39" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S39" s="9" t="n">
-        <v>1</v>
+      <c r="S39" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T39" s="9" t="n">
         <v>0</v>
@@ -6285,10 +6285,10 @@
         <v>16</v>
       </c>
       <c r="J58" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
@@ -6670,13 +6670,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L62" s="8" t="inlineStr">
         <is>
@@ -6715,7 +6715,7 @@
         <v>0</v>
       </c>
       <c r="V62" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W62" s="9" t="n">
         <v>0</v>
@@ -8319,13 +8319,13 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L79" s="8" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         </is>
       </c>
       <c r="P92" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q92" s="9" t="n">
         <v>0</v>
@@ -9774,13 +9774,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L94" s="8" t="inlineStr">
         <is>
@@ -9871,13 +9871,13 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L95" s="8" t="inlineStr">
         <is>
@@ -9916,7 +9916,7 @@
         <v>0</v>
       </c>
       <c r="V95" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W95" s="9" t="n">
         <v>0</v>
@@ -10747,10 +10747,10 @@
         <v>15</v>
       </c>
       <c r="J104" s="4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="L104" s="8" t="inlineStr">
         <is>
@@ -11714,13 +11714,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L114" s="4" t="inlineStr">
         <is>
@@ -11741,7 +11741,7 @@
         </is>
       </c>
       <c r="P114" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q114" s="9" t="n">
         <v>1</v>
@@ -11759,7 +11759,7 @@
         <v>0</v>
       </c>
       <c r="V114" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W114" s="9" t="n">
         <v>0</v>
@@ -11811,13 +11811,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="L115" s="4" t="inlineStr">
         <is>
@@ -11859,7 +11859,7 @@
         <v>4</v>
       </c>
       <c r="W115" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X115" s="10" t="n">
         <v>7</v>
@@ -11911,10 +11911,10 @@
         <v>4</v>
       </c>
       <c r="J116" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="L116" s="8" t="inlineStr">
         <is>
@@ -12975,13 +12975,13 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J127" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L127" s="8" t="inlineStr">
         <is>
@@ -13155,7 +13155,7 @@
         </is>
       </c>
       <c r="E129" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F129" s="6" t="n">
         <v>10</v>
@@ -13169,13 +13169,13 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J129" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L129" s="4" t="inlineStr">
         <is>
@@ -13216,8 +13216,8 @@
       <c r="V129" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W129" s="9" t="n">
-        <v>3</v>
+      <c r="W129" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X129" s="10" t="n">
         <v>5</v>
@@ -13557,13 +13557,13 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J133" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L133" s="8" t="inlineStr">
         <is>
@@ -13945,13 +13945,13 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J137" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L137" s="8" t="inlineStr">
         <is>
@@ -14045,10 +14045,10 @@
         <v>16</v>
       </c>
       <c r="J138" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="L138" s="8" t="inlineStr">
         <is>
@@ -14457,7 +14457,7 @@
         </is>
       </c>
       <c r="P142" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q142" s="9" t="n">
         <v>0</v>
@@ -14610,7 +14610,7 @@
         </is>
       </c>
       <c r="E144" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F144" s="6" t="n">
         <v>10</v>
@@ -14624,13 +14624,13 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J144" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L144" s="4" t="inlineStr">
         <is>
@@ -14651,7 +14651,7 @@
         </is>
       </c>
       <c r="P144" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q144" s="9" t="n">
         <v>0</v>
@@ -14665,8 +14665,8 @@
       <c r="T144" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U144" s="9" t="n">
-        <v>0</v>
+      <c r="U144" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V144" s="10" t="n">
         <v>4</v>
@@ -15524,7 +15524,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -16085,13 +16085,13 @@
         <v>6</v>
       </c>
       <c r="D27" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -16184,7 +16184,7 @@
         <v>6</v>
       </c>
       <c r="D30" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
